--- a/create_forecast_basic/future/JTMT/Intermediates/240703_pop_2045_jtmt.xlsx
+++ b/create_forecast_basic/future/JTMT/Intermediates/240703_pop_2045_jtmt.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>1444.080822634002</v>
+        <v>1444.080822634</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>4412.522397006568</v>
+        <v>4412.522397006571</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>3901.367990122833</v>
+        <v>3901.367990122837</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>17983.19477202056</v>
+        <v>17983.19477202055</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>10199.10228034708</v>
+        <v>10199.10228034707</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>17699.37028065899</v>
+        <v>17699.370280659</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>11418.56142226344</v>
+        <v>11418.56142226343</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>46872.6379749994</v>
+        <v>46872.63797499942</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>34651.02399823596</v>
+        <v>34651.02399823593</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>11597.75028165577</v>
+        <v>11597.75028165578</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>1703.392588127761</v>
+        <v>1703.392588127763</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>8345.658044192278</v>
+        <v>8345.65804419228</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>2903.105744298144</v>
+        <v>2903.105744298145</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>2633.019057977311</v>
+        <v>2633.019057977313</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>15044.84024666124</v>
+        <v>15044.84024666123</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>11624.59464468694</v>
+        <v>11624.59464468695</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>3548.080350829619</v>
+        <v>3548.080350829617</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>8810.887690708556</v>
+        <v>8810.88769070854</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>8128.135535092119</v>
+        <v>8128.135535092116</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>43393.29712199598</v>
+        <v>43393.29712199599</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>11595.35987802437</v>
+        <v>11595.35987802438</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>14653.03333363161</v>
+        <v>14653.0333336316</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>31470.66957178908</v>
+        <v>31470.66957178909</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>7041.977550501426</v>
+        <v>7041.97755050143</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>5935.048125165347</v>
+        <v>5935.048125165346</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>4657.342380594495</v>
+        <v>4657.342380594494</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>735.6036983263888</v>
+        <v>735.6036983263886</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>4199.883524368045</v>
+        <v>4199.883524368048</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>2763.651896216311</v>
+        <v>2763.65189621631</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>4690.264028814986</v>
+        <v>4690.264028814987</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>7943.44135986974</v>
+        <v>7943.441359869738</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>3934.831287525574</v>
+        <v>3934.831287525576</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>3148.423261427506</v>
+        <v>3148.423261427505</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>4877.257729121437</v>
+        <v>4877.257729121438</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>5454.23730935279</v>
+        <v>5454.237309352789</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>6258.93970246337</v>
+        <v>6258.939702463372</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
-        <v>9273.087630376784</v>
+        <v>9273.08763037678</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>6493.841006380268</v>
+        <v>6493.841006380267</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>8122.207414731325</v>
+        <v>8122.207414731324</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>62254.81556662309</v>
+        <v>62254.81556662313</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
-        <v>53962.0471183341</v>
+        <v>53962.04711833408</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>57616.60941373192</v>
+        <v>57616.60941373189</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>61606.43346297648</v>
+        <v>61606.43346297649</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="n">
-        <v>74898.71422240316</v>
+        <v>74898.71422240317</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>93618.99641204368</v>
+        <v>93618.99641204359</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>1976.098917533337</v>
+        <v>1976.098917533336</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>17292.06600795573</v>
+        <v>17292.06600795571</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>9973.504387042964</v>
+        <v>9973.504387042969</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>3749.14178402223</v>
+        <v>3749.141784022229</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>4960.237872431137</v>
+        <v>4960.237872431138</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>12625.18061057271</v>
+        <v>12625.1806105727</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>16309.7897959832</v>
+        <v>16309.78979598319</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>5882.23659663767</v>
+        <v>5882.236596637671</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>31913.94072700108</v>
+        <v>31913.94072700106</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>19659.32741983673</v>
+        <v>19659.32741983675</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>78383.27457355097</v>
+        <v>78383.27457355105</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>13573.5575709857</v>
+        <v>13573.55757098569</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>25347.97654026994</v>
+        <v>25347.97654026995</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>32362.97343742904</v>
+        <v>32362.97343742902</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>45289.63472859195</v>
+        <v>45289.63472859196</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>9261.975369723456</v>
+        <v>9261.975369723457</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>11127.81900875665</v>
+        <v>11127.81900875666</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>7393.235028499726</v>
+        <v>7393.235028499724</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>3983.447116632477</v>
+        <v>3983.447116632479</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>4495.305652546583</v>
+        <v>4495.305652546584</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>11724.78187801683</v>
+        <v>11724.78187801682</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>93861.23325926118</v>
+        <v>93861.23325926115</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>14082.38300421123</v>
+        <v>14082.38300421121</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>8140.752313540292</v>
+        <v>8140.752313540289</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>50679.54837240438</v>
+        <v>50679.54837240437</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>34747.33964562143</v>
+        <v>34747.33964562141</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>48056.83231222583</v>
+        <v>48056.83231222588</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>35996.89549938603</v>
+        <v>35996.89549938602</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
